--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.85029980000001</v>
+        <v>5.081580000000001</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>51.51096958009323</v>
+        <v>5.283727352200225</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>63.87912183973153</v>
+        <v>6.9624197849523</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>89.54358378087241</v>
+        <v>11.5182880646589</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>112.9441589299607</v>
+        <v>11.64137297826347</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>149.9752258967847</v>
+        <v>15.32716277317509</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>137.9142733767429</v>
+        <v>15.53125555989227</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>121.6096866900579</v>
+        <v>12.57220147667866</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>137.829301281083</v>
+        <v>11.39386848655085</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>128.2876359813482</v>
+        <v>9.493633420105111</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114.3005304299919</v>
+        <v>7.838439861345225</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>110.7898555478524</v>
+        <v>7.672197517248391</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>121.2404495550408</v>
+        <v>8.190366981118542</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>123.8780433815223</v>
+        <v>8.367853498931664</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>118.8310094079374</v>
+        <v>7.939330818419856</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>104.8883210793124</v>
+        <v>7.269663080306969</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>94.33947149008523</v>
+        <v>6.170089243300461</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>88.88376586274939</v>
+        <v>5.597498212310537</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>84.72533283377089</v>
+        <v>5.12281717829857</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>74.64257020306746</v>
+        <v>4.749072759326581</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>67.53116023213546</v>
+        <v>4.190121162371145</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>63.51014336643722</v>
+        <v>4.037209247435933</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>59.52859028549337</v>
+        <v>3.998538408145445</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>55.39253937810384</v>
+        <v>3.804840621672571</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>54.17080369220357</v>
+        <v>3.543578639109895</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>51.14130726004714</v>
+        <v>3.384811457729339</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>46.89534678210217</v>
+        <v>3.135095423074342</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>41.24794963274755</v>
+        <v>2.857732683570959</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>36.74446407471269</v>
+        <v>2.637436389527764</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>32.10250898721589</v>
+        <v>2.399896568684803</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>28.7450654727088</v>
+        <v>2.166647737235454</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>26.32136578185024</v>
+        <v>1.974866631536436</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>23.94947621611365</v>
+        <v>1.742060093929921</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>21.81274078280267</v>
+        <v>1.620983527033796</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>19.80148111528926</v>
+        <v>1.495444400459195</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>18.03577842747327</v>
+        <v>1.378001278838641</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>16.65311826870946</v>
+        <v>1.297253970084066</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>15.69069230462861</v>
+        <v>1.24555313776437</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>14.81026543240217</v>
+        <v>1.140750031453967</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>14.45715672716815</v>
+        <v>1.04974386415347</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>14.07654897389609</v>
+        <v>1.026975781810865</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>13.7302782313695</v>
+        <v>0.9877485239985504</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>12.66470792172915</v>
+        <v>0.9332939982697906</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>11.48755956800276</v>
+        <v>0.866382740115327</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>10.91551696573213</v>
+        <v>0.8244818454923677</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>10.51531949893928</v>
+        <v>0.7933211721681508</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>10.12617864681803</v>
+        <v>0.7604156739494067</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>9.857575404862727</v>
+        <v>0.7293716418886415</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>9.41797685359232</v>
+        <v>0.695258052702293</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>9.497033453011211</v>
+        <v>0.6594100256616863</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>9.401285943428791</v>
+        <v>0.6257928795039857</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>9.057770694688749</v>
+        <v>0.5956407341308492</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>8.545612473727415</v>
+        <v>0.5716677482861958</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>8.099122478730731</v>
+        <v>0.5710261941221904</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>7.640851482753455</v>
+        <v>0.5822668397826519</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>7.20560500976492</v>
+        <v>0.5915089468592378</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>6.972720595881837</v>
+        <v>0.5935914646544741</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>6.80024962901262</v>
+        <v>0.5888493002301713</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>6.645838837177902</v>
+        <v>0.5904539991751874</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>6.466605364182565</v>
+        <v>0.5919957319708704</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>6.264070428816154</v>
+        <v>0.5839940870163689</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>6.0834267257214</v>
+        <v>0.5771401440928784</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>5.92368738234279</v>
+        <v>0.5666286052549332</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>5.759372007629069</v>
+        <v>0.5487581659144932</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>5.607762313926558</v>
+        <v>0.5374679690143551</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>5.455109451509005</v>
+        <v>0.522529016629134</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>5.336430916287838</v>
+        <v>0.5063681262674331</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>5.276547373530578</v>
+        <v>0.4951099493579766</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>5.167797593319826</v>
+        <v>0.4780498790842728</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>5.011448742437556</v>
+        <v>0.455021675068759</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>4.816487351414908</v>
+        <v>0.4276297608610297</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>4.648635489201545</v>
+        <v>0.4089388828141435</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>4.492829772975092</v>
+        <v>0.3907669557485242</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>4.381875154948999</v>
+        <v>0.3794192649568728</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>4.282160821380211</v>
+        <v>0.369746791517437</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>4.220968730537219</v>
+        <v>0.3590545601014201</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>4.146741111264795</v>
+        <v>0.3475970344690898</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>4.046866982653359</v>
+        <v>0.3356691602866076</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>3.92032283315864</v>
+        <v>0.323523631545054</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>3.778932942234896</v>
+        <v>0.3113502100071738</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>3.72966675899118</v>
+        <v>0.2994892575849769</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>3.67223650006022</v>
+        <v>0.28805264194948</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>3.604624230960298</v>
+        <v>0.2769827975526647</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>3.526534885586991</v>
+        <v>0.2662746963579491</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>3.442494344258077</v>
+        <v>0.2563552520145365</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>3.354214163821865</v>
+        <v>0.2472880989254143</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>3.263880135174047</v>
+        <v>0.2391646513078454</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>3.167624396769853</v>
+        <v>0.2314422016878908</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>3.065460182565164</v>
+        <v>0.2239693620668383</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>2.95843162340236</v>
+        <v>0.2167048578322671</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>2.85118688574378</v>
+        <v>0.2099860304509405</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>2.749604010927422</v>
+        <v>0.2042887729556073</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>2.660412028906976</v>
+        <v>0.2001886241444956</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>2.57027595883942</v>
+        <v>0.1962383179605373</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>2.4800799392193</v>
+        <v>0.1924097604361086</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>2.428884284346309</v>
+        <v>0.1886828481383466</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>2.390063795346427</v>
+        <v>0.1850466488199227</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>2.346398234242778</v>
+        <v>0.1814813640990248</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>2.298520440713728</v>
+        <v>0.1779730088433</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>2.246408492197856</v>
+        <v>0.1745088711976608</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>2.190538693150343</v>
+        <v>0.1710808051357349</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>2.131575149550262</v>
+        <v>0.1676840286075931</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>2.069892418344934</v>
+        <v>0.1643161017602695</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>2.012440139318707</v>
+        <v>0.160976587232557</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>1.959086141796045</v>
+        <v>0.1576666819648723</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>1.916678752628524</v>
+        <v>0.1543888448764109</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>1.874725340514498</v>
+        <v>0.1511464391427255</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>1.831961430957119</v>
+        <v>0.1479434026669937</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>1.788571586395266</v>
+        <v>0.1447839557892666</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>1.744743939820648</v>
+        <v>0.1416723514291393</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>1.700665227666456</v>
+        <v>0.1386126697287184</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>1.656516616131159</v>
+        <v>0.1356086567776972</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>1.612470341437017</v>
+        <v>0.132663605180028</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>1.568692596706453</v>
+        <v>0.1297802729337052</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>1.525358485272406</v>
+        <v>0.126960836257979</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>1.482558224323586</v>
+        <v>0.1242068715832291</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>1.447033166936295</v>
+        <v>0.1215193617943969</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>1.412514694138405</v>
+        <v>0.1188987218845769</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>1.386233525531929</v>
+        <v>0.1163464749801828</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>1.360831868368518</v>
+        <v>0.1138608397806119</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>1.335443200180884</v>
+        <v>0.1114414635980649</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>1.310126490072594</v>
+        <v>0.1090928759387075</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>1.284937736593837</v>
+        <v>0.1068108664281275</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>1.259929458944453</v>
+        <v>0.104588816186159</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>1.23702307840315</v>
+        <v>0.1026155730254321</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>1.214338973114784</v>
+        <v>0.1006928255501958</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>1.191923528362302</v>
+        <v>0.09881896705223429</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>1.172941265243669</v>
+        <v>0.09731066908402843</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>1.154847832715357</v>
+        <v>0.09590312240084532</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>1.137121538194149</v>
+        <v>0.09453818961057837</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>1.11977835589664</v>
+        <v>0.09321304364862444</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>1.102838290537373</v>
+        <v>0.09192577434514933</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>1.086315728213138</v>
+        <v>0.09067439991317316</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>1.070243621224368</v>
+        <v>0.08945919971931238</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>1.054606310986343</v>
+        <v>0.08827608817585206</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>1.039394613643513</v>
+        <v>0.08712260062364184</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>1.024608008904649</v>
+        <v>0.08599673331456251</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>1.010242024283323</v>
+        <v>0.08489652850050568</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.9962845148509837</v>
+        <v>0.08382009039088194</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.9837544019312731</v>
+        <v>0.08276559868627437</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.9721245583564129</v>
+        <v>0.08173131977032773</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.960493789402821</v>
+        <v>0.08071561567005919</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.9488845218495809</v>
+        <v>0.07971695092787802</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.9373131449860096</v>
+        <v>0.07873389752762198</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.9257904353635098</v>
+        <v>0.07776513805539825</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.9143220927725763</v>
+        <v>0.07680946724545441</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.9029093533968164</v>
+        <v>0.07586579210069208</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.8915496496444661</v>
+        <v>0.07493313074763597</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.8802446461139485</v>
+        <v>0.07401061019335264</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.8689883005100741</v>
+        <v>0.07309746315171202</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.8577608087543982</v>
+        <v>0.07219302407725144</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8465512004734879</v>
+        <v>0.0712967245592302</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.835347881345439</v>
+        <v>0.07040808820702359</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.8247147865143482</v>
+        <v>0.06952672513570866</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.8149878016355864</v>
+        <v>0.06865232618305646</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.8053856343722848</v>
+        <v>0.06778465693005335</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.7958966422211938</v>
+        <v>0.06692355164005966</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.786510251623556</v>
+        <v>0.06606967086301624</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.7772169485438347</v>
+        <v>0.06522512226132235</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.7680082585484136</v>
+        <v>0.06438688033802649</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.7588767182504191</v>
+        <v>0.06355499807277809</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.7498158393303377</v>
+        <v>0.06272956765722384</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.7408200667055801</v>
+        <v>0.06191071514836961</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.7318847319021436</v>
+        <v>0.06109859537514595</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.7230060028541878</v>
+        <v>0.06029338712229518</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.7141808311047746</v>
+        <v>0.05949528860829573</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.7061344084990275</v>
+        <v>0.05877867342558887</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.7035081798758333</v>
+        <v>0.05861706808364636</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.7006293821071627</v>
+        <v>0.05843254643113159</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.6974427835480487</v>
+        <v>0.05821976251140375</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.6939199756191361</v>
+        <v>0.05797605418257372</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.6900584319707581</v>
+        <v>0.05770134991099834</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.6858188586081814</v>
+        <v>0.0573917852567727</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.6821971186273795</v>
+        <v>0.05714897433623789</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.681777187589375</v>
+        <v>0.05701485322696569</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.6815914756174383</v>
+        <v>0.05686195761130092</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.681102991904618</v>
+        <v>0.05668908714101816</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.6802945901456046</v>
+        <v>0.0564953021026811</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.6791542655730157</v>
+        <v>0.05627991253809354</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6776731058943828</v>
+        <v>0.05604246576911306</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.6758451611265859</v>
+        <v>0.05578273263751057</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.67366729502553</v>
+        <v>0.05550069273790839</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.6751321684549439</v>
+        <v>0.05560356751442257</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.6766380142945354</v>
+        <v>0.05572435164459465</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.6773346644099733</v>
+        <v>0.05577645632928772</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.6771948728104649</v>
+        <v>0.05575710906281047</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.6762017944362484</v>
+        <v>0.05566453114825722</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.6743652519716627</v>
+        <v>0.05549878851254028</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.6716787780678809</v>
+        <v>0.05525944066456069</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.6681458482774341</v>
+        <v>0.05494702435115179</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.6637859060069993</v>
+        <v>0.05456324017428179</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.658625692675171</v>
+        <v>0.05411048608867438</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6526984132806299</v>
+        <v>0.05359177670920409</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.6460428780551163</v>
+        <v>0.05301066017236982</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.6407684664481992</v>
+        <v>0.05258171827055119</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.6367977804693142</v>
+        <v>0.0522965903910733</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.6323325679902455</v>
+        <v>0.05197154808824439</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.6273763664985965</v>
+        <v>0.0516083643964085</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.621984523295478</v>
+        <v>0.05121010435046139</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6161535790700753</v>
+        <v>0.05077586780880304</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.6099249645224663</v>
+        <v>0.05030932031952198</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.283727352200225</v>
+        <v>5.22227094954159</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>6.9624197849523</v>
+        <v>5.915419894416161</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>11.5182880646589</v>
+        <v>7.115718007242877</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.64137297826347</v>
+        <v>9.187489967957161</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>15.32716277317509</v>
+        <v>11.84855290419675</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>15.53125555989227</v>
+        <v>13.56272515258661</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>12.57220147667866</v>
+        <v>13.30403658759759</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>11.39386848655085</v>
+        <v>14.11106876028937</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>9.493633420105111</v>
+        <v>13.87634331174932</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>7.838439861345225</v>
+        <v>11.80651455676606</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>7.672197517248391</v>
+        <v>10.90355265843229</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>8.190366981118542</v>
+        <v>10.67590931940048</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>8.367853498931664</v>
+        <v>10.24664076903253</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>7.939330818419856</v>
+        <v>10.34223957161214</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>7.269663080306969</v>
+        <v>9.682916466219682</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>6.170089243300461</v>
+        <v>9.611436483772229</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>5.597498212310537</v>
+        <v>9.884446291985551</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>5.12281717829857</v>
+        <v>10.15845635308879</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>4.749072759326581</v>
+        <v>9.663251413717099</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>4.190121162371145</v>
+        <v>8.687084276362899</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>4.037209247435933</v>
+        <v>8.603615686093171</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>3.998538408145445</v>
+        <v>8.33799935759354</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>3.804840621672571</v>
+        <v>7.776457410351065</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>3.543578639109895</v>
+        <v>7.38120998113318</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>3.384811457729339</v>
+        <v>6.774731045353644</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>3.135095423074342</v>
+        <v>6.07693891469255</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>2.857732683570959</v>
+        <v>5.257939465303702</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>2.637436389527764</v>
+        <v>4.55975906909247</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>2.399896568684803</v>
+        <v>4.018548711660187</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>2.166647737235454</v>
+        <v>3.663001632015821</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>1.974866631536436</v>
+        <v>3.30912860518111</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>1.742060093929921</v>
+        <v>2.953788011341699</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>1.620983527033796</v>
+        <v>2.743021694133318</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>1.495444400459195</v>
+        <v>2.529928027440689</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>1.378001278838641</v>
+        <v>2.365756411870103</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>1.297253970084066</v>
+        <v>2.225341080173788</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>1.24555313776437</v>
+        <v>2.098700269375531</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>1.140750031453967</v>
+        <v>1.929900221742342</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.04974386415347</v>
+        <v>1.797577138537531</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>1.026975781810865</v>
+        <v>1.688758897451459</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9877485239985504</v>
+        <v>1.589032156097571</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9332939982697906</v>
+        <v>1.454645613913557</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>0.866382740115327</v>
+        <v>1.328161377011953</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8244818454923677</v>
+        <v>1.273488158365756</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7933211721681508</v>
+        <v>1.225244847054883</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7604156739494067</v>
+        <v>1.177326356598897</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7293716418886415</v>
+        <v>1.140815896330291</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.695258052702293</v>
+        <v>1.08639599094862</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6594100256616863</v>
+        <v>1.085171653589076</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6257928795039857</v>
+        <v>1.066607017987958</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5956407341308492</v>
+        <v>1.026240290273495</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5716677482861958</v>
+        <v>0.9710347276698916</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5710261941221904</v>
+        <v>0.9179119485810384</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5822668397826519</v>
+        <v>0.8682855858869265</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5915089468592378</v>
+        <v>0.8184866886852326</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5935914646544741</v>
+        <v>0.7838203501014941</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5888493002301713</v>
+        <v>0.7515102278581388</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5904539991751874</v>
+        <v>0.7320903011144505</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5919957319708704</v>
+        <v>0.7124469929623312</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5839940870163689</v>
+        <v>0.6873081753674347</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5771401440928784</v>
+        <v>0.6675405520530888</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5666286052549332</v>
+        <v>0.648322128350507</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5487581659144932</v>
+        <v>0.624131510720664</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5374679690143551</v>
+        <v>0.6069199535691238</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.522529016629134</v>
+        <v>0.5877799071089632</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5063681262674331</v>
+        <v>0.5675865055021992</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4951099493579766</v>
+        <v>0.5464656667301804</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4780498790842728</v>
+        <v>0.5241643440330903</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.455021675068759</v>
+        <v>0.5011676133690024</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4276297608610297</v>
+        <v>0.4781235579142283</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4089388828141435</v>
+        <v>0.4612800442070203</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3907669557485242</v>
+        <v>0.4439286946670948</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3794192649568728</v>
+        <v>0.4289837758174044</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.369746791517437</v>
+        <v>0.4192968067111991</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3590545601014201</v>
+        <v>0.4146236537719388</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3475970344690898</v>
+        <v>0.4094574152136415</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3356691602866076</v>
+        <v>0.4021918480546461</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.323523631545054</v>
+        <v>0.3925371291370666</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3113502100071738</v>
+        <v>0.381482462171943</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2994892575849769</v>
+        <v>0.3796717957180994</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.28805264194948</v>
+        <v>0.3767575513019586</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2769827975526647</v>
+        <v>0.3726696906060758</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2662746963579491</v>
+        <v>0.3673689302471922</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2563552520145365</v>
+        <v>0.360966804668239</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2472880989254143</v>
+        <v>0.3535415221426115</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2391646513078454</v>
+        <v>0.345939594621728</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2314422016878908</v>
+        <v>0.3377331463944206</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2239693620668383</v>
+        <v>0.3289383658043277</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2167048578322671</v>
+        <v>0.3196888912493129</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2099860304509405</v>
+        <v>0.3101047012117868</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2042887729556073</v>
+        <v>0.3002912016713998</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2001886241444956</v>
+        <v>0.290340444405995</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1962383179605373</v>
+        <v>0.280322355739547</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1924097604361086</v>
+        <v>0.2703380875621486</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1886828481383466</v>
+        <v>0.2643737463336836</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1850466488199227</v>
+        <v>0.2597121637119023</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1814813640990248</v>
+        <v>0.2546055537330622</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1779730088433</v>
+        <v>0.2491247247343721</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1745088711976608</v>
+        <v>0.2432690609987454</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1710808051357349</v>
+        <v>0.237087540947841</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1676840286075931</v>
+        <v>0.2306471050984966</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1643161017602695</v>
+        <v>0.2239840804955768</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.160976587232557</v>
+        <v>0.2178040757250606</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1576666819648723</v>
+        <v>0.2120900116012613</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1543888448764109</v>
+        <v>0.2075357769103623</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1511464391427255</v>
+        <v>0.2030671711873159</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1479434026669937</v>
+        <v>0.198550463672422</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1447839557892666</v>
+        <v>0.1939995892343991</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1416723514291393</v>
+        <v>0.1894289568868776</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1386126697287184</v>
+        <v>0.1848530746769119</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1356086567776972</v>
+        <v>0.18028623002127</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.132663605180028</v>
+        <v>0.1757447737075292</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1297802729337052</v>
+        <v>0.1712426099130181</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.126960836257979</v>
+        <v>0.1667918731526012</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1242068715832291</v>
+        <v>0.1623995329121126</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1215193617943969</v>
+        <v>0.1587510716696985</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1188987218845769</v>
+        <v>0.155206271493414</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1163464749801828</v>
+        <v>0.1525014531177994</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1138608397806119</v>
+        <v>0.1498862458899203</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1114414635980649</v>
+        <v>0.1472734001859188</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1090928759387075</v>
+        <v>0.1446740348236014</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1068108664281275</v>
+        <v>0.1420884799537085</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.104588816186159</v>
+        <v>0.1395228697152654</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1026155730254321</v>
+        <v>0.1371739895174633</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1006928255501958</v>
+        <v>0.1348503625146086</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.09881896705223429</v>
+        <v>0.1325547986183316</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.09731066908402843</v>
+        <v>0.130292504859306</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.09590312240084532</v>
+        <v>0.128069895519552</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.09453818961057837</v>
+        <v>0.1258903625522139</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.09321304364862444</v>
+        <v>0.1237564932689837</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.09192577434514933</v>
+        <v>0.1216713424373227</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.09067439991317316</v>
+        <v>0.1196374218194153</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.08945919971931238</v>
+        <v>0.1176568357884533</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.08827608817585206</v>
+        <v>0.1157310629880029</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.08712260062364184</v>
+        <v>0.1138605893420773</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.08599673331456251</v>
+        <v>0.1120462950606781</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.08489652850050568</v>
+        <v>0.1102885875931195</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.08382009039088194</v>
+        <v>0.1085870106225359</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.08276559868627437</v>
+        <v>0.1070468599083858</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.08173131977032773</v>
+        <v>0.1056178332411582</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.08071561567005919</v>
+        <v>0.1042049013415982</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.07971695092787802</v>
+        <v>0.1028107358344533</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.07873389752762198</v>
+        <v>0.1014372867577839</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.07776513805539825</v>
+        <v>0.1000858267044242</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.07680946724545441</v>
+        <v>0.09875700772036336</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.07586579210069208</v>
+        <v>0.09745092728802034</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.07493313074763597</v>
+        <v>0.0961672000936039</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.07401061019335264</v>
+        <v>0.09490578252709976</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.07309746315171202</v>
+        <v>0.09366576165810296</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.07219302407725144</v>
+        <v>0.09244474452622026</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0712967245592302</v>
+        <v>0.09124116831684</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.07040808820702359</v>
+        <v>0.09005334336303998</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.06952672513570866</v>
+        <v>0.08893819157119483</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.06865232618305646</v>
+        <v>0.08792933934315501</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.06778465693005335</v>
+        <v>0.08694648976142333</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.06692355164005966</v>
+        <v>0.08598776670999485</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.06606967086301624</v>
+        <v>0.0850522712679159</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.06522512226132235</v>
+        <v>0.08414399122513967</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.06438688033802649</v>
+        <v>0.08325451153106735</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.06355499807277809</v>
+        <v>0.08238231195878223</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.06272956765722384</v>
+        <v>0.08152596709929094</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.06191071514836961</v>
+        <v>0.08068414703203439</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.06109859537514595</v>
+        <v>0.07985561709904027</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.06029338712229518</v>
+        <v>0.07903923690415775</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.05949528860829573</v>
+        <v>0.07823395864162785</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.05877867342558887</v>
+        <v>0.07743882484771883</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.05861706808364636</v>
+        <v>0.07665296566678216</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.05843254643113159</v>
+        <v>0.07587559571631539</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.05821976251140375</v>
+        <v>0.07510601063802164</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.05797605418257372</v>
+        <v>0.07434358337583911</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.05770134991099834</v>
+        <v>0.07360991206005014</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0573917852567727</v>
+        <v>0.07290254876069202</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.05714897433623789</v>
+        <v>0.07219808881549757</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.05701485322696569</v>
+        <v>0.07171789659696669</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.05686195761130092</v>
+        <v>0.07128683849619306</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.05668908714101816</v>
+        <v>0.07085129375015325</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0564953021026811</v>
+        <v>0.07041038053226684</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.05627991253809354</v>
+        <v>0.06996349869869589</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.05604246576911306</v>
+        <v>0.06951013248303553</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.05578273263751057</v>
+        <v>0.06904985016369181</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.05550069273790839</v>
+        <v>0.06858230291334819</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.05560356751442257</v>
+        <v>0.06810722294361055</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.05572435164459465</v>
+        <v>0.06762442102191897</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.05577645632928772</v>
+        <v>0.06713433670669668</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.05575710906281047</v>
+        <v>0.06663762269914025</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.05566453114825722</v>
+        <v>0.06613302664953688</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.05549878851254028</v>
+        <v>0.06562233946734063</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.05525944066456069</v>
+        <v>0.06510478722841122</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.05494702435115179</v>
+        <v>0.06457976644272941</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.05456324017428179</v>
+        <v>0.06404752792971516</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.05411048608867438</v>
+        <v>0.06350836913636208</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.05359177670920409</v>
+        <v>0.06296262952571276</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.05301066017236982</v>
+        <v>0.06241068600561896</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.05258171827055119</v>
+        <v>0.06185294842688217</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0522965903910733</v>
+        <v>0.06128985519863357</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.05197154808824439</v>
+        <v>0.0607219447447807</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0516083643964085</v>
+        <v>0.06015162969552423</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.05121010435046139</v>
+        <v>0.05957736699551961</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05077586780880304</v>
+        <v>0.05899966920192869</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.05030932031952198</v>
+        <v>0.05841905784022176</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.22227094954159</v>
+        <v>5.261663322626752</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>5.915419894416161</v>
+        <v>6.000810168609518</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>7.115718007242877</v>
+        <v>8.375736499102082</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.187489967957161</v>
+        <v>9.621492073520622</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>11.84855290419675</v>
+        <v>14.13187951710295</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>13.56272515258661</v>
+        <v>15.39693911437982</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>13.30403658759759</v>
+        <v>13.2118711073135</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>14.11106876028937</v>
+        <v>12.05712745699875</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>13.87634331174932</v>
+        <v>12.03907574337383</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>11.80651455676606</v>
+        <v>9.93402470708701</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>10.90355265843229</v>
+        <v>9.498598842623421</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>10.67590931940048</v>
+        <v>9.563770515396733</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>10.24664076903253</v>
+        <v>9.398465890331563</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>10.34223957161214</v>
+        <v>9.113310090623735</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>9.682916466219682</v>
+        <v>8.251844604461954</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>9.611436483772229</v>
+        <v>8.12458896664891</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>9.884446291985551</v>
+        <v>8.115669959420757</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>10.15845635308879</v>
+        <v>8.006480280016872</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>9.663251413717099</v>
+        <v>7.910581519177185</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>8.687084276362899</v>
+        <v>7.106711695692701</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>8.603615686093171</v>
+        <v>7.073192967968223</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>8.33799935759354</v>
+        <v>6.810510436500906</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>7.776457410351065</v>
+        <v>6.362519274673588</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>7.38120998113318</v>
+        <v>5.850555525348531</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>6.774731045353644</v>
+        <v>5.409565827591659</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>6.07693891469255</v>
+        <v>4.900609599575858</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>5.257939465303702</v>
+        <v>4.37056292586929</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>4.55975906909247</v>
+        <v>3.935780713742052</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>4.018548711660187</v>
+        <v>3.606270799347143</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>3.663001632015821</v>
+        <v>3.268140140910827</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>3.30912860518111</v>
+        <v>2.942370216161152</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>2.953788011341699</v>
+        <v>2.601386999776768</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>2.743021694133318</v>
+        <v>2.414789660009715</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>2.529928027440689</v>
+        <v>2.209331529507797</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>2.365756411870103</v>
+        <v>2.025732406249421</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>2.225341080173788</v>
+        <v>1.893511725878893</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>2.098700269375531</v>
+        <v>1.778231670160941</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>1.929900221742342</v>
+        <v>1.618363429622397</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.797577138537531</v>
+        <v>1.482113662239504</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>1.688758897451459</v>
+        <v>1.413188882524019</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>1.589032156097571</v>
+        <v>1.330251803100342</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>1.454645613913557</v>
+        <v>1.236377955325098</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>1.328161377011953</v>
+        <v>1.138444087991127</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.273488158365756</v>
+        <v>1.076640065072095</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.225244847054883</v>
+        <v>1.039514212088766</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>1.177326356598897</v>
+        <v>0.9983167439129804</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>1.140815896330291</v>
+        <v>0.9547078666737236</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>1.08639599094862</v>
+        <v>0.9093551383543621</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>1.085171653589076</v>
+        <v>0.8650542867416752</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1.066607017987958</v>
+        <v>0.8257958109995551</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>1.026240290273495</v>
+        <v>0.7897650279083041</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9710347276698916</v>
+        <v>0.7597526154821559</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9179119485810384</v>
+        <v>0.7529920898694542</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8682855858869265</v>
+        <v>0.7581162284080595</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8184866886852326</v>
+        <v>0.7610868525693643</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7838203501014941</v>
+        <v>0.7568043081374908</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7515102278581388</v>
+        <v>0.7457076251401575</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7320903011144505</v>
+        <v>0.7403771506788955</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7124469929623312</v>
+        <v>0.7321976562763941</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6873081753674347</v>
+        <v>0.7157904383942119</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6675405520530888</v>
+        <v>0.7019410909654183</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.648322128350507</v>
+        <v>0.685824625349221</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.624131510720664</v>
+        <v>0.6635066178416219</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6069199535691238</v>
+        <v>0.6487718581661894</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5877799071089632</v>
+        <v>0.6311396422167995</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5675865055021992</v>
+        <v>0.6136118545851894</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5464656667301804</v>
+        <v>0.5995581179645437</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5241643440330903</v>
+        <v>0.5788500482776647</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5011676133690024</v>
+        <v>0.5523919619408487</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4781235579142283</v>
+        <v>0.5218044817821333</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4612800442070203</v>
+        <v>0.5001534502374201</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4439286946670948</v>
+        <v>0.4792435507140679</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4289837758174044</v>
+        <v>0.465348630507081</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4192968067111991</v>
+        <v>0.4532856431189454</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4146236537719388</v>
+        <v>0.4403398199482592</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4094574152136415</v>
+        <v>0.4267364202295711</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4021918480546461</v>
+        <v>0.4127465286371199</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3925371291370666</v>
+        <v>0.3986056449369372</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.381482462171943</v>
+        <v>0.3844930798778926</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3796717957180994</v>
+        <v>0.3707446280456697</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3767575513019586</v>
+        <v>0.3574720457676274</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3726696906060758</v>
+        <v>0.3446204644939049</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3673689302471922</v>
+        <v>0.3321886002868156</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.360966804668239</v>
+        <v>0.3205970847283457</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3535415221426115</v>
+        <v>0.3099230840441163</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.345939594621728</v>
+        <v>0.300259009473034</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3377331463944206</v>
+        <v>0.2910612585606576</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3289383658043277</v>
+        <v>0.2821757394144169</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3196888912493129</v>
+        <v>0.2735569609346723</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3101047012117868</v>
+        <v>0.2655369603454819</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3002912016713998</v>
+        <v>0.2585857154710587</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.290340444405995</v>
+        <v>0.2532727054793393</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.280322355739547</v>
+        <v>0.2481448713464213</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2703380875621486</v>
+        <v>0.2432037452482993</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2643737463336836</v>
+        <v>0.2396922587102784</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2597121637119023</v>
+        <v>0.2361103361575697</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2546055537330622</v>
+        <v>0.2324372164032122</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2491247247343721</v>
+        <v>0.2286616407537937</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2432690609987454</v>
+        <v>0.2247768933360222</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.237087540947841</v>
+        <v>0.2207836051777124</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2306471050984966</v>
+        <v>0.2166932255048186</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2239840804955768</v>
+        <v>0.2125237452240532</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2178040757250606</v>
+        <v>0.2082744415073512</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.2120900116012613</v>
+        <v>0.203960853681898</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.2075357769103623</v>
+        <v>0.1995999527406303</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2030671711873159</v>
+        <v>0.1952093615690179</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.198550463672422</v>
+        <v>0.1908066737090883</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1939995892343991</v>
+        <v>0.1864088845231484</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1894289568868776</v>
+        <v>0.1820319402043998</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1848530746769119</v>
+        <v>0.1776904031180215</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.18028623002127</v>
+        <v>0.1733972264833006</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1757447737075292</v>
+        <v>0.169166174061294</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1712426099130181</v>
+        <v>0.1650069192468305</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1667918731526012</v>
+        <v>0.1609241948656941</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1623995329121126</v>
+        <v>0.156924032823218</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1587510716696985</v>
+        <v>0.1536860873324061</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.155206271493414</v>
+        <v>0.1505639719281691</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1525014531177994</v>
+        <v>0.1475221740997792</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1498862458899203</v>
+        <v>0.1445582448914133</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1472734001859188</v>
+        <v>0.1416711183443366</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1446740348236014</v>
+        <v>0.1388634643902489</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1420884799537085</v>
+        <v>0.1361269280338971</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1395228697152654</v>
+        <v>0.133458912273795</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1371739895174633</v>
+        <v>0.1310475942649315</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1348503625146086</v>
+        <v>0.1286931579984535</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1325547986183316</v>
+        <v>0.1263904664361813</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.130292504859306</v>
+        <v>0.1244596596710281</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.128069895519552</v>
+        <v>0.12263551034499</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1258903625522139</v>
+        <v>0.1208595349884841</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1237564932689837</v>
+        <v>0.1191286311455637</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1216713424373227</v>
+        <v>0.1174406809136865</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1196374218194153</v>
+        <v>0.1157935580728018</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1176568357884533</v>
+        <v>0.1141874554914328</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1157310629880029</v>
+        <v>0.112618252945794</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1138605893420773</v>
+        <v>0.1110834964857479</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1120462950606781</v>
+        <v>0.1095812316876764</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1102885875931195</v>
+        <v>0.1081095819973318</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1085870106225359</v>
+        <v>0.1066667580905294</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1070468599083858</v>
+        <v>0.1052518045036152</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1056178332411582</v>
+        <v>0.103865964566674</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1042049013415982</v>
+        <v>0.1025040914826974</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1028107358344533</v>
+        <v>0.1011647985957779</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1014372867577839</v>
+        <v>0.09984680468760418</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1000858267044242</v>
+        <v>0.09854893331344954</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.09875700772036336</v>
+        <v>0.09727011107416386</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.09745092728802034</v>
+        <v>0.09600936500499699</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0961672000936039</v>
+        <v>0.09476581921998956</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.09490578252709976</v>
+        <v>0.09353869094547919</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.09366576165810296</v>
+        <v>0.09232728608218112</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.09244474452622026</v>
+        <v>0.09113099438947074</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.09124116831684</v>
+        <v>0.0899492844078594</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.09005334336303998</v>
+        <v>0.08878169821009579</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.08893819157119483</v>
+        <v>0.08762784604313367</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.08792933934315501</v>
+        <v>0.08648740095981396</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.08694648976142333</v>
+        <v>0.08536009346439644</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.08598776670999485</v>
+        <v>0.08424570625936098</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0850522712679159</v>
+        <v>0.08314496547283419</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.08414399122513967</v>
+        <v>0.08206343975539844</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08325451153106735</v>
+        <v>0.08099424188036117</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.08238231195878223</v>
+        <v>0.07993731902983221</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08152596709929094</v>
+        <v>0.07889264676705315</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.08068414703203439</v>
+        <v>0.07786022493575009</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.07985561709904027</v>
+        <v>0.07684007380291255</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.07903923690415775</v>
+        <v>0.0758322304613241</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.07823395864162785</v>
+        <v>0.07483674549254112</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.07743882484771883</v>
+        <v>0.07392784004891619</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.07665296566678216</v>
+        <v>0.07357888448567776</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.07587559571631539</v>
+        <v>0.07321179381388415</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.07510601063802164</v>
+        <v>0.07282106152563086</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.07434358337583911</v>
+        <v>0.07240382664457028</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.07360991206005014</v>
+        <v>0.0719798978435002</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.07290254876069202</v>
+        <v>0.07154547957034658</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.07219808881549757</v>
+        <v>0.0711790396971899</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.07171789659696669</v>
+        <v>0.07092255217965183</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.07128683849619306</v>
+        <v>0.07065007843331296</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.07085129375015325</v>
+        <v>0.07035911607956247</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.07041038053226684</v>
+        <v>0.0700485448076321</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.06996349869869589</v>
+        <v>0.06971768609415245</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.06951013248303553</v>
+        <v>0.06936609340896065</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.06904985016369181</v>
+        <v>0.06899353898565007</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.06858230291334819</v>
+        <v>0.06859999955983508</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.06810722294361055</v>
+        <v>0.06859268994709224</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.06762442102191897</v>
+        <v>0.06860459488042861</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.06713433670669668</v>
+        <v>0.06854966596961307</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06663762269914025</v>
+        <v>0.06842580967589734</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.06613302664953688</v>
+        <v>0.06822995082149312</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.06562233946734063</v>
+        <v>0.06796213656966399</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.06510478722841122</v>
+        <v>0.06762190620351873</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.06457976644272941</v>
+        <v>0.06720977507295342</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.06404752792971516</v>
+        <v>0.0667274214784669</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.06350836913636208</v>
+        <v>0.066177220411042</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.06296262952571276</v>
+        <v>0.06556216307679107</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.06241068600561896</v>
+        <v>0.06488577395503368</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.06185294842688217</v>
+        <v>0.06436261110581175</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.06128985519863357</v>
+        <v>0.06398429026457453</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0607219447447807</v>
+        <v>0.06356705954927061</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.06015162969552423</v>
+        <v>0.06311266889095829</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.05957736699551961</v>
+        <v>0.06262416065737313</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05899966920192869</v>
+        <v>0.06210061256165133</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.05841905784022176</v>
+        <v>0.06154566860133628</v>
       </c>
     </row>
   </sheetData>

--- a/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
+++ b/Python for Project Work SRE_Part 2/ERS/ERS/ERS_Means/SA_el_hor2_mean.xlsx
@@ -464,7 +464,7 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>5.261663322626752</v>
+        <v>5.258801482404588</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>6.000810168609518</v>
+        <v>6.525028280958971</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>8.375736499102082</v>
+        <v>9.345822569747202</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>12.5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.621492073520622</v>
+        <v>9.856234818214009</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>14.13187951710295</v>
+        <v>11.93035521302183</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>15.39693911437982</v>
+        <v>12.96140173045463</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>7.142857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>13.2118711073135</v>
+        <v>13.54011810745267</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>6.25</v>
       </c>
       <c r="C10" t="n">
-        <v>12.05712745699875</v>
+        <v>13.37001484936901</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>5.555555555555555</v>
       </c>
       <c r="C11" t="n">
-        <v>12.03907574337383</v>
+        <v>13.91661867755498</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>9.93402470708701</v>
+        <v>12.06330779736691</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>4.545454545454546</v>
       </c>
       <c r="C13" t="n">
-        <v>9.498598842623421</v>
+        <v>10.71670475950998</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>4.166666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>9.563770515396733</v>
+        <v>10.78921071903246</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>3.846153846153846</v>
       </c>
       <c r="C15" t="n">
-        <v>9.398465890331563</v>
+        <v>10.17557888658744</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>3.571428571428571</v>
       </c>
       <c r="C16" t="n">
-        <v>9.113310090623735</v>
+        <v>9.8118092903114</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>8.251844604461954</v>
+        <v>8.961295546880649</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>3.125</v>
       </c>
       <c r="C18" t="n">
-        <v>8.12458896664891</v>
+        <v>8.944934089712575</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>2.941176470588235</v>
       </c>
       <c r="C19" t="n">
-        <v>8.115669959420757</v>
+        <v>9.373392293864104</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="C20" t="n">
-        <v>8.006480280016872</v>
+        <v>9.746273526272141</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="C21" t="n">
-        <v>7.910581519177185</v>
+        <v>9.213908826257834</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>2.5</v>
       </c>
       <c r="C22" t="n">
-        <v>7.106711695692701</v>
+        <v>8.11064376510596</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>2.380952380952381</v>
       </c>
       <c r="C23" t="n">
-        <v>7.073192967968223</v>
+        <v>7.884642662618132</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>2.272727272727273</v>
       </c>
       <c r="C24" t="n">
-        <v>6.810510436500906</v>
+        <v>7.648071769395324</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>2.173913043478261</v>
       </c>
       <c r="C25" t="n">
-        <v>6.362519274673588</v>
+        <v>7.13243340379585</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>2.083333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>5.850555525348531</v>
+        <v>6.854828407048361</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>5.409565827591659</v>
+        <v>6.313753626678958</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>1.923076923076923</v>
       </c>
       <c r="C28" t="n">
-        <v>4.900609599575858</v>
+        <v>5.661689323895757</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>1.851851851851852</v>
       </c>
       <c r="C29" t="n">
-        <v>4.37056292586929</v>
+        <v>4.870221381193239</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>1.785714285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>3.935780713742052</v>
+        <v>4.24047661607721</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>1.724137931034483</v>
       </c>
       <c r="C31" t="n">
-        <v>3.606270799347143</v>
+        <v>3.73261374794714</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>3.268140140910827</v>
+        <v>3.40822038339654</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1.612903225806452</v>
       </c>
       <c r="C33" t="n">
-        <v>2.942370216161152</v>
+        <v>3.070425834227356</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>2.601386999776768</v>
+        <v>2.728412450227462</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>1.515151515151515</v>
       </c>
       <c r="C35" t="n">
-        <v>2.414789660009715</v>
+        <v>2.531893970562172</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>1.470588235294118</v>
       </c>
       <c r="C36" t="n">
-        <v>2.209331529507797</v>
+        <v>2.352121380056056</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>1.428571428571428</v>
       </c>
       <c r="C37" t="n">
-        <v>2.025732406249421</v>
+        <v>2.214363152828827</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>1.388888888888889</v>
       </c>
       <c r="C38" t="n">
-        <v>1.893511725878893</v>
+        <v>2.091504285325333</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>1.351351351351351</v>
       </c>
       <c r="C39" t="n">
-        <v>1.778231670160941</v>
+        <v>1.967819421065768</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="C40" t="n">
-        <v>1.618363429622397</v>
+        <v>1.800693460220739</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>1.282051282051282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.482113662239504</v>
+        <v>1.666551054015935</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>1.413188882524019</v>
+        <v>1.563199225277267</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>1.219512195121951</v>
       </c>
       <c r="C43" t="n">
-        <v>1.330251803100342</v>
+        <v>1.470661648522734</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>1.19047619047619</v>
       </c>
       <c r="C44" t="n">
-        <v>1.236377955325098</v>
+        <v>1.343194428610344</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1.162790697674419</v>
       </c>
       <c r="C45" t="n">
-        <v>1.138444087991127</v>
+        <v>1.22345147022275</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>1.136363636363636</v>
       </c>
       <c r="C46" t="n">
-        <v>1.076640065072095</v>
+        <v>1.175299798666104</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="C47" t="n">
-        <v>1.039514212088766</v>
+        <v>1.133333044278652</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>1.08695652173913</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9983167439129804</v>
+        <v>1.091422600173505</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>1.063829787234043</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9547078666737236</v>
+        <v>1.06313119980063</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1.041666666666667</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9093551383543621</v>
+        <v>1.013623016350428</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>1.020408163265306</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8650542867416752</v>
+        <v>1.015263724180876</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8257958109995551</v>
+        <v>1.001497968974353</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>0.9803921568627451</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7897650279083041</v>
+        <v>0.9657021111767973</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>0.9615384615384615</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7597526154821559</v>
+        <v>0.914082457719652</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0.9433962264150942</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7529920898694542</v>
+        <v>0.8558747788594276</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0.9259259259259258</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7581162284080595</v>
+        <v>0.8030889976252902</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7610868525693643</v>
+        <v>0.7519424177791535</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0.8928571428571428</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7568043081374908</v>
+        <v>0.7176558745999445</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>0.8771929824561403</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7457076251401575</v>
+        <v>0.6873294482879485</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0.8620689655172414</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7403771506788955</v>
+        <v>0.6720028898064631</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>0.8474576271186441</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7321976562763941</v>
+        <v>0.6606559450221642</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7157904383942119</v>
+        <v>0.643775231388711</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0.819672131147541</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7019410909654183</v>
+        <v>0.627504693492853</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>0.8064516129032259</v>
       </c>
       <c r="C64" t="n">
-        <v>0.685824625349221</v>
+        <v>0.6071314540438995</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6635066178416219</v>
+        <v>0.5814835177079716</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0.78125</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6487718581661894</v>
+        <v>0.5626242964813457</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6311396422167995</v>
+        <v>0.5416762397687485</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0.7575757575757576</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6136118545851894</v>
+        <v>0.5189135564261556</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0.7462686567164178</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5995581179645437</v>
+        <v>0.4960304645196224</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>0.7352941176470588</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5788500482776647</v>
+        <v>0.4731339041992992</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0.7246376811594202</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5523919619408487</v>
+        <v>0.4497860679562242</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0.7142857142857142</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5218044817821333</v>
+        <v>0.4265577557438381</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0.7042253521126761</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5001534502374201</v>
+        <v>0.4097238283944683</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>0.6944444444444444</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4792435507140679</v>
+        <v>0.3925751725286528</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>0.684931506849315</v>
       </c>
       <c r="C75" t="n">
-        <v>0.465348630507081</v>
+        <v>0.378037371902783</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0.6756756756756757</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4532856431189454</v>
+        <v>0.3689686080587212</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4403398199482592</v>
+        <v>0.3650939519770825</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4267364202295711</v>
+        <v>0.36088453848463</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0.6493506493506493</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4127465286371199</v>
+        <v>0.3547534627141151</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>0.641025641025641</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3986056449369372</v>
+        <v>0.3463472917940074</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0.6329113924050632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3844930798778926</v>
+        <v>0.3366920990450737</v>
       </c>
     </row>
     <row r="82">
@@ -1333,7 +1333,7 @@
         <v>0.625</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3707446280456697</v>
+        <v>0.336365718860293</v>
       </c>
     </row>
     <row r="83">
@@ -1344,7 +1344,7 @@
         <v>0.6172839506172839</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3574720457676274</v>
+        <v>0.3350478110660039</v>
       </c>
     </row>
     <row r="84">
@@ -1355,7 +1355,7 @@
         <v>0.6097560975609756</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3446204644939049</v>
+        <v>0.3326027182995989</v>
       </c>
     </row>
     <row r="85">
@@ -1366,7 +1366,7 @@
         <v>0.6024096385542168</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3321886002868156</v>
+        <v>0.329016005352806</v>
       </c>
     </row>
     <row r="86">
@@ -1377,7 +1377,7 @@
         <v>0.5952380952380952</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3205970847283457</v>
+        <v>0.3243495224179778</v>
       </c>
     </row>
     <row r="87">
@@ -1388,7 +1388,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3099230840441163</v>
+        <v>0.3186869317127676</v>
       </c>
     </row>
     <row r="88">
@@ -1399,7 +1399,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="C88" t="n">
-        <v>0.300259009473034</v>
+        <v>0.312152574820552</v>
       </c>
     </row>
     <row r="89">
@@ -1410,7 +1410,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2910612585606576</v>
+        <v>0.3048833967324455</v>
       </c>
     </row>
     <row r="90">
@@ -1421,7 +1421,7 @@
         <v>0.5681818181818182</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2821757394144169</v>
+        <v>0.2970171146443897</v>
       </c>
     </row>
     <row r="91">
@@ -1432,7 +1432,7 @@
         <v>0.5617977528089888</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2735569609346723</v>
+        <v>0.2886838950091077</v>
       </c>
     </row>
     <row r="92">
@@ -1443,7 +1443,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2655369603454819</v>
+        <v>0.2800011641698536</v>
       </c>
     </row>
     <row r="93">
@@ -1454,7 +1454,7 @@
         <v>0.5494505494505494</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2585857154710587</v>
+        <v>0.2710725956459485</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
         <v>0.5434782608695652</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2532727054793393</v>
+        <v>0.261989197512908</v>
       </c>
     </row>
     <row r="95">
@@ -1476,7 +1476,7 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2481448713464213</v>
+        <v>0.2528203971485322</v>
       </c>
     </row>
     <row r="96">
@@ -1487,7 +1487,7 @@
         <v>0.5319148936170213</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2432037452482993</v>
+        <v>0.2436672493309677</v>
       </c>
     </row>
     <row r="97">
@@ -1498,7 +1498,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2396922587102784</v>
+        <v>0.2385160337481862</v>
       </c>
     </row>
     <row r="98">
@@ -1509,7 +1509,7 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2361103361575697</v>
+        <v>0.2346499122456721</v>
       </c>
     </row>
     <row r="99">
@@ -1520,7 +1520,7 @@
         <v>0.5154639175257733</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2324372164032122</v>
+        <v>0.230321494244963</v>
       </c>
     </row>
     <row r="100">
@@ -1531,7 +1531,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2286616407537937</v>
+        <v>0.2255992823998784</v>
       </c>
     </row>
     <row r="101">
@@ -1542,7 +1542,7 @@
         <v>0.5050505050505051</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2247768933360222</v>
+        <v>0.220485464838664</v>
       </c>
     </row>
     <row r="102">
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2207836051777124</v>
+        <v>0.2150299914406173</v>
       </c>
     </row>
     <row r="103">
@@ -1564,7 +1564,7 @@
         <v>0.495049504950495</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2166932255048186</v>
+        <v>0.2092999433401306</v>
       </c>
     </row>
     <row r="104">
@@ -1575,7 +1575,7 @@
         <v>0.4901960784313725</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2125237452240532</v>
+        <v>0.2033316974879948</v>
       </c>
     </row>
     <row r="105">
@@ -1586,7 +1586,7 @@
         <v>0.4854368932038835</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2082744415073512</v>
+        <v>0.1978308306958989</v>
       </c>
     </row>
     <row r="106">
@@ -1597,7 +1597,7 @@
         <v>0.4807692307692307</v>
       </c>
       <c r="C106" t="n">
-        <v>0.203960853681898</v>
+        <v>0.1927801657934292</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1995999527406303</v>
+        <v>0.1888734465173224</v>
       </c>
     </row>
     <row r="108">
@@ -1619,7 +1619,7 @@
         <v>0.4716981132075471</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1952093615690179</v>
+        <v>0.1850363008226901</v>
       </c>
     </row>
     <row r="109">
@@ -1630,7 +1630,7 @@
         <v>0.4672897196261682</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1908066737090883</v>
+        <v>0.1811348199718418</v>
       </c>
     </row>
     <row r="110">
@@ -1641,7 +1641,7 @@
         <v>0.4629629629629629</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1864088845231484</v>
+        <v>0.177182772875326</v>
       </c>
     </row>
     <row r="111">
@@ -1652,7 +1652,7 @@
         <v>0.4587155963302752</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1820319402043998</v>
+        <v>0.1731944304389594</v>
       </c>
     </row>
     <row r="112">
@@ -1663,7 +1663,7 @@
         <v>0.4545454545454545</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1776904031180215</v>
+        <v>0.1691842031930884</v>
       </c>
     </row>
     <row r="113">
@@ -1674,7 +1674,7 @@
         <v>0.4504504504504504</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1733972264833006</v>
+        <v>0.1651663310904377</v>
       </c>
     </row>
     <row r="114">
@@ -1685,7 +1685,7 @@
         <v>0.4464285714285714</v>
       </c>
       <c r="C114" t="n">
-        <v>0.169166174061294</v>
+        <v>0.1611571737347489</v>
       </c>
     </row>
     <row r="115">
@@ -1696,7 +1696,7 @@
         <v>0.4424778761061947</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1650069192468305</v>
+        <v>0.157170703615374</v>
       </c>
     </row>
     <row r="116">
@@ -1707,7 +1707,7 @@
         <v>0.4385964912280702</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1609241948656941</v>
+        <v>0.153219183599434</v>
       </c>
     </row>
     <row r="117">
@@ -1718,7 +1718,7 @@
         <v>0.4347826086956521</v>
       </c>
       <c r="C117" t="n">
-        <v>0.156924032823218</v>
+        <v>0.1493097698473847</v>
       </c>
     </row>
     <row r="118">
@@ -1729,7 +1729,7 @@
         <v>0.4310344827586207</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1536860873324061</v>
+        <v>0.1461281862907901</v>
       </c>
     </row>
     <row r="119">
@@ -1740,7 +1740,7 @@
         <v>0.4273504273504274</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1505639719281691</v>
+        <v>0.143034506304034</v>
       </c>
     </row>
     <row r="120">
@@ -1751,7 +1751,7 @@
         <v>0.4237288135593221</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1475221740997792</v>
+        <v>0.140763750426966</v>
       </c>
     </row>
     <row r="121">
@@ -1762,7 +1762,7 @@
         <v>0.4201680672268908</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1445582448914133</v>
+        <v>0.1385671136808428</v>
       </c>
     </row>
     <row r="122">
@@ -1773,7 +1773,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1416711183443366</v>
+        <v>0.1363581543162002</v>
       </c>
     </row>
     <row r="123">
@@ -1784,7 +1784,7 @@
         <v>0.4132231404958678</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1388634643902489</v>
+        <v>0.1341495573660778</v>
       </c>
     </row>
     <row r="124">
@@ -1795,7 +1795,7 @@
         <v>0.4098360655737705</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1361269280338971</v>
+        <v>0.1319455243047541</v>
       </c>
     </row>
     <row r="125">
@@ -1806,7 +1806,7 @@
         <v>0.4065040650406504</v>
       </c>
       <c r="C125" t="n">
-        <v>0.133458912273795</v>
+        <v>0.1297479277538739</v>
       </c>
     </row>
     <row r="126">
@@ -1817,7 +1817,7 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1310475942649315</v>
+        <v>0.127563125158329</v>
       </c>
     </row>
     <row r="127">
@@ -1828,7 +1828,7 @@
         <v>0.4</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1286931579984535</v>
+        <v>0.1253971437907124</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>0.3968253968253968</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1263904664361813</v>
+        <v>0.1232556134398974</v>
       </c>
     </row>
     <row r="129">
@@ -1850,7 +1850,7 @@
         <v>0.3937007874015748</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1244596596710281</v>
+        <v>0.1211437139011705</v>
       </c>
     </row>
     <row r="130">
@@ -1861,7 +1861,7 @@
         <v>0.390625</v>
       </c>
       <c r="C130" t="n">
-        <v>0.12263551034499</v>
+        <v>0.1190661363612689</v>
       </c>
     </row>
     <row r="131">
@@ -1872,7 +1872,7 @@
         <v>0.3875968992248062</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1208595349884841</v>
+        <v>0.117027057598335</v>
       </c>
     </row>
     <row r="132">
@@ -1883,7 +1883,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1191286311455637</v>
+        <v>0.1150301257703204</v>
       </c>
     </row>
     <row r="133">
@@ -1894,7 +1894,7 @@
         <v>0.3816793893129771</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1174406809136865</v>
+        <v>0.113078456508009</v>
       </c>
     </row>
     <row r="134">
@@ -1905,7 +1905,7 @@
         <v>0.3787878787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1157935580728018</v>
+        <v>0.1111746379984281</v>
       </c>
     </row>
     <row r="135">
@@ -1916,7 +1916,7 @@
         <v>0.3759398496240601</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1141874554914328</v>
+        <v>0.1093208640836731</v>
       </c>
     </row>
     <row r="136">
@@ -1927,7 +1927,7 @@
         <v>0.3731343283582089</v>
       </c>
       <c r="C136" t="n">
-        <v>0.112618252945794</v>
+        <v>0.1075187134902729</v>
       </c>
     </row>
     <row r="137">
@@ -1938,7 +1938,7 @@
         <v>0.3703703703703703</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1110834964857479</v>
+        <v>0.1057687805346826</v>
       </c>
     </row>
     <row r="138">
@@ -1949,7 +1949,7 @@
         <v>0.3676470588235294</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1095812316876764</v>
+        <v>0.104072059978523</v>
       </c>
     </row>
     <row r="139">
@@ -1960,7 +1960,7 @@
         <v>0.364963503649635</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1081095819973318</v>
+        <v>0.1024290780045872</v>
       </c>
     </row>
     <row r="140">
@@ -1971,7 +1971,7 @@
         <v>0.3623188405797101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1066667580905294</v>
+        <v>0.1008394994203398</v>
       </c>
     </row>
     <row r="141">
@@ -1982,7 +1982,7 @@
         <v>0.3597122302158273</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1052518045036152</v>
+        <v>0.09940874190081549</v>
       </c>
     </row>
     <row r="142">
@@ -1993,7 +1993,7 @@
         <v>0.3571428571428571</v>
       </c>
       <c r="C142" t="n">
-        <v>0.103865964566674</v>
+        <v>0.09808662453653073</v>
       </c>
     </row>
     <row r="143">
@@ -2004,7 +2004,7 @@
         <v>0.3546099290780142</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1025040914826974</v>
+        <v>0.09677823751479073</v>
       </c>
     </row>
     <row r="144">
@@ -2015,7 +2015,7 @@
         <v>0.3521126760563381</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1011647985957779</v>
+        <v>0.09548636905830836</v>
       </c>
     </row>
     <row r="145">
@@ -2026,7 +2026,7 @@
         <v>0.3496503496503497</v>
       </c>
       <c r="C145" t="n">
-        <v>0.09984680468760418</v>
+        <v>0.09421308207281685</v>
       </c>
     </row>
     <row r="146">
@@ -2037,7 +2037,7 @@
         <v>0.3472222222222222</v>
       </c>
       <c r="C146" t="n">
-        <v>0.09854893331344954</v>
+        <v>0.09295975758849286</v>
       </c>
     </row>
     <row r="147">
@@ -2048,7 +2048,7 @@
         <v>0.3448275862068966</v>
       </c>
       <c r="C147" t="n">
-        <v>0.09727011107416386</v>
+        <v>0.09172715110860725</v>
       </c>
     </row>
     <row r="148">
@@ -2059,7 +2059,7 @@
         <v>0.3424657534246575</v>
       </c>
       <c r="C148" t="n">
-        <v>0.09600936500499699</v>
+        <v>0.0905154581797989</v>
       </c>
     </row>
     <row r="149">
@@ -2070,7 +2070,7 @@
         <v>0.3401360544217687</v>
       </c>
       <c r="C149" t="n">
-        <v>0.09476581921998956</v>
+        <v>0.08932438586966374</v>
       </c>
     </row>
     <row r="150">
@@ -2081,7 +2081,7 @@
         <v>0.3378378378378378</v>
       </c>
       <c r="C150" t="n">
-        <v>0.09353869094547919</v>
+        <v>0.0881539770871622</v>
       </c>
     </row>
     <row r="151">
@@ -2092,7 +2092,7 @@
         <v>0.3355704697986577</v>
       </c>
       <c r="C151" t="n">
-        <v>0.09232728608218112</v>
+        <v>0.08700339947503966</v>
       </c>
     </row>
     <row r="152">
@@ -2103,7 +2103,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="C152" t="n">
-        <v>0.09113099438947074</v>
+        <v>0.08587033470179183</v>
       </c>
     </row>
     <row r="153">
@@ -2114,7 +2114,7 @@
         <v>0.3311258278145696</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0899492844078594</v>
+        <v>0.08475328871014046</v>
       </c>
     </row>
     <row r="154">
@@ -2125,7 +2125,7 @@
         <v>0.3289473684210527</v>
       </c>
       <c r="C154" t="n">
-        <v>0.08878169821009579</v>
+        <v>0.08365063485248884</v>
       </c>
     </row>
     <row r="155">
@@ -2136,7 +2136,7 @@
         <v>0.326797385620915</v>
       </c>
       <c r="C155" t="n">
-        <v>0.08762784604313367</v>
+        <v>0.08261935250094091</v>
       </c>
     </row>
     <row r="156">
@@ -2147,7 +2147,7 @@
         <v>0.3246753246753247</v>
       </c>
       <c r="C156" t="n">
-        <v>0.08648740095981396</v>
+        <v>0.08169312019287753</v>
       </c>
     </row>
     <row r="157">
@@ -2158,7 +2158,7 @@
         <v>0.3225806451612903</v>
       </c>
       <c r="C157" t="n">
-        <v>0.08536009346439644</v>
+        <v>0.08079168807367348</v>
       </c>
     </row>
     <row r="158">
@@ -2169,7 +2169,7 @@
         <v>0.3205128205128205</v>
       </c>
       <c r="C158" t="n">
-        <v>0.08424570625936098</v>
+        <v>0.07991322229642543</v>
       </c>
     </row>
     <row r="159">
@@ -2180,7 +2180,7 @@
         <v>0.3184713375796178</v>
       </c>
       <c r="C159" t="n">
-        <v>0.08314496547283419</v>
+        <v>0.07905686171363201</v>
       </c>
     </row>
     <row r="160">
@@ -2191,7 +2191,7 @@
         <v>0.3164556962025316</v>
       </c>
       <c r="C160" t="n">
-        <v>0.08206343975539844</v>
+        <v>0.07822662770010895</v>
       </c>
     </row>
     <row r="161">
@@ -2202,7 +2202,7 @@
         <v>0.3144654088050314</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08099424188036117</v>
+        <v>0.07741413491588008</v>
       </c>
     </row>
     <row r="162">
@@ -2213,7 +2213,7 @@
         <v>0.3125</v>
       </c>
       <c r="C162" t="n">
-        <v>0.07993731902983221</v>
+        <v>0.07661788928396519</v>
       </c>
     </row>
     <row r="163">
@@ -2224,7 +2224,7 @@
         <v>0.3105590062111801</v>
       </c>
       <c r="C163" t="n">
-        <v>0.07889264676705315</v>
+        <v>0.07583648829627138</v>
       </c>
     </row>
     <row r="164">
@@ -2235,7 +2235,7 @@
         <v>0.308641975308642</v>
       </c>
       <c r="C164" t="n">
-        <v>0.07786022493575009</v>
+        <v>0.07506862198884408</v>
       </c>
     </row>
     <row r="165">
@@ -2246,7 +2246,7 @@
         <v>0.3067484662576687</v>
       </c>
       <c r="C165" t="n">
-        <v>0.07684007380291255</v>
+        <v>0.07431307301173334</v>
       </c>
     </row>
     <row r="166">
@@ -2257,7 +2257,7 @@
         <v>0.3048780487804878</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0758322304613241</v>
+        <v>0.07356871591331827</v>
       </c>
     </row>
     <row r="167">
@@ -2268,7 +2268,7 @@
         <v>0.303030303030303</v>
       </c>
       <c r="C167" t="n">
-        <v>0.07483674549254112</v>
+        <v>0.07283451574008283</v>
       </c>
     </row>
     <row r="168">
@@ -2279,7 +2279,7 @@
         <v>0.3012048192771084</v>
       </c>
       <c r="C168" t="n">
-        <v>0.07392784004891619</v>
+        <v>0.07210952604591699</v>
       </c>
     </row>
     <row r="169">
@@ -2290,7 +2290,7 @@
         <v>0.2994011976047904</v>
       </c>
       <c r="C169" t="n">
-        <v>0.07357888448567776</v>
+        <v>0.07139288640075749</v>
       </c>
     </row>
     <row r="170">
@@ -2301,7 +2301,7 @@
         <v>0.2976190476190476</v>
       </c>
       <c r="C170" t="n">
-        <v>0.07321179381388415</v>
+        <v>0.07068381948240772</v>
       </c>
     </row>
     <row r="171">
@@ -2312,7 +2312,7 @@
         <v>0.2958579881656805</v>
       </c>
       <c r="C171" t="n">
-        <v>0.07282106152563086</v>
+        <v>0.06998162783756258</v>
       </c>
     </row>
     <row r="172">
@@ -2323,7 +2323,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="C172" t="n">
-        <v>0.07240382664457028</v>
+        <v>0.06928569035529977</v>
       </c>
     </row>
     <row r="173">
@@ -2334,7 +2334,7 @@
         <v>0.2923976608187134</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0719798978435002</v>
+        <v>0.06861761032911159</v>
       </c>
     </row>
     <row r="174">
@@ -2345,7 +2345,7 @@
         <v>0.2906976744186047</v>
       </c>
       <c r="C174" t="n">
-        <v>0.07154547957034658</v>
+        <v>0.06797494437329146</v>
       </c>
     </row>
     <row r="175">
@@ -2356,7 +2356,7 @@
         <v>0.2890173410404624</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0711790396971899</v>
+        <v>0.06733429189858792</v>
       </c>
     </row>
     <row r="176">
@@ -2367,7 +2367,7 @@
         <v>0.2873563218390804</v>
       </c>
       <c r="C176" t="n">
-        <v>0.07092255217965183</v>
+        <v>0.06691702101174123</v>
       </c>
     </row>
     <row r="177">
@@ -2378,7 +2378,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="C177" t="n">
-        <v>0.07065007843331296</v>
+        <v>0.06654800161846217</v>
       </c>
     </row>
     <row r="178">
@@ -2389,7 +2389,7 @@
         <v>0.2840909090909091</v>
       </c>
       <c r="C178" t="n">
-        <v>0.07035911607956247</v>
+        <v>0.0661736163555124</v>
       </c>
     </row>
     <row r="179">
@@ -2400,7 +2400,7 @@
         <v>0.2824858757062147</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0700485448076321</v>
+        <v>0.06579298677422592</v>
       </c>
     </row>
     <row r="180">
@@ -2411,7 +2411,7 @@
         <v>0.2808988764044944</v>
       </c>
       <c r="C180" t="n">
-        <v>0.06971768609415245</v>
+        <v>0.06540551616690683</v>
       </c>
     </row>
     <row r="181">
@@ -2422,7 +2422,7 @@
         <v>0.2793296089385475</v>
       </c>
       <c r="C181" t="n">
-        <v>0.06936609340896065</v>
+        <v>0.06501069233147141</v>
       </c>
     </row>
     <row r="182">
@@ -2433,7 +2433,7 @@
         <v>0.2777777777777778</v>
       </c>
       <c r="C182" t="n">
-        <v>0.06899353898565007</v>
+        <v>0.06460808729747121</v>
       </c>
     </row>
     <row r="183">
@@ -2444,7 +2444,7 @@
         <v>0.2762430939226519</v>
       </c>
       <c r="C183" t="n">
-        <v>0.06859999955983508</v>
+        <v>0.06419735622552217</v>
       </c>
     </row>
     <row r="184">
@@ -2455,7 +2455,7 @@
         <v>0.2747252747252747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.06859268994709224</v>
+        <v>0.06377823559196732</v>
       </c>
     </row>
     <row r="185">
@@ -2466,7 +2466,7 @@
         <v>0.273224043715847</v>
       </c>
       <c r="C185" t="n">
-        <v>0.06860459488042861</v>
+        <v>0.06335054073891988</v>
       </c>
     </row>
     <row r="186">
@@ -2477,7 +2477,7 @@
         <v>0.2717391304347826</v>
       </c>
       <c r="C186" t="n">
-        <v>0.06854966596961307</v>
+        <v>0.06291471613459652</v>
       </c>
     </row>
     <row r="187">
@@ -2488,7 +2488,7 @@
         <v>0.2702702702702702</v>
       </c>
       <c r="C187" t="n">
-        <v>0.06842580967589734</v>
+        <v>0.06247141974359595</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>0.2688172043010753</v>
       </c>
       <c r="C188" t="n">
-        <v>0.06822995082149312</v>
+        <v>0.06201940484546315</v>
       </c>
     </row>
     <row r="189">
@@ -2510,7 +2510,7 @@
         <v>0.267379679144385</v>
       </c>
       <c r="C189" t="n">
-        <v>0.06796213656966399</v>
+        <v>0.06155957979161482</v>
       </c>
     </row>
     <row r="190">
@@ -2521,7 +2521,7 @@
         <v>0.2659574468085106</v>
       </c>
       <c r="C190" t="n">
-        <v>0.06762190620351873</v>
+        <v>0.06109170017797734</v>
       </c>
     </row>
     <row r="191">
@@ -2532,7 +2532,7 @@
         <v>0.2645502645502645</v>
       </c>
       <c r="C191" t="n">
-        <v>0.06720977507295342</v>
+        <v>0.06061555893221336</v>
       </c>
     </row>
     <row r="192">
@@ -2543,7 +2543,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0667274214784669</v>
+        <v>0.0601314135413963</v>
       </c>
     </row>
     <row r="193">
@@ -2554,7 +2554,7 @@
         <v>0.2617801047120419</v>
       </c>
       <c r="C193" t="n">
-        <v>0.066177220411042</v>
+        <v>0.05963956848933432</v>
       </c>
     </row>
     <row r="194">
@@ -2565,7 +2565,7 @@
         <v>0.2604166666666667</v>
       </c>
       <c r="C194" t="n">
-        <v>0.06556216307679107</v>
+        <v>0.05914037063349493</v>
       </c>
     </row>
     <row r="195">
@@ -2576,7 +2576,7 @@
         <v>0.2590673575129534</v>
       </c>
       <c r="C195" t="n">
-        <v>0.06488577395503368</v>
+        <v>0.05863420461981032</v>
       </c>
     </row>
     <row r="196">
@@ -2587,7 +2587,7 @@
         <v>0.2577319587628866</v>
       </c>
       <c r="C196" t="n">
-        <v>0.06436261110581175</v>
+        <v>0.05812148836562069</v>
       </c>
     </row>
     <row r="197">
@@ -2598,7 +2598,7 @@
         <v>0.2564102564102564</v>
       </c>
       <c r="C197" t="n">
-        <v>0.06398429026457453</v>
+        <v>0.05760266865718559</v>
       </c>
     </row>
     <row r="198">
@@ -2609,7 +2609,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="C198" t="n">
-        <v>0.06356705954927061</v>
+        <v>0.05707829258799454</v>
       </c>
     </row>
     <row r="199">
@@ -2620,7 +2620,7 @@
         <v>0.2538071065989848</v>
       </c>
       <c r="C199" t="n">
-        <v>0.06311266889095829</v>
+        <v>0.05655078173119312</v>
       </c>
     </row>
     <row r="200">
@@ -2631,7 +2631,7 @@
         <v>0.2525252525252525</v>
       </c>
       <c r="C200" t="n">
-        <v>0.06262416065737313</v>
+        <v>0.05601860222699662</v>
       </c>
     </row>
     <row r="201">
@@ -2642,7 +2642,7 @@
         <v>0.2512562814070352</v>
       </c>
       <c r="C201" t="n">
-        <v>0.06210061256165133</v>
+        <v>0.05548227606069309</v>
       </c>
     </row>
     <row r="202">
@@ -2653,7 +2653,7 @@
         <v>0.25</v>
       </c>
       <c r="C202" t="n">
-        <v>0.06154566860133628</v>
+        <v>0.05494233439735358</v>
       </c>
     </row>
   </sheetData>
